--- a/stories/arbres/ATOM-EMO.LEX.008-02.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.008-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Noé est à l'école. Maman aide pour un atelier. Noé porte un bol d'eau. Le bol penche. L'eau tombe sur la table. Noé sent ses joues chaudes. Il dit : je suis gêné. C'est une erreur. Une erreur ne dit pas qui il est. Être gêné, ce n'est pas honteux. Maman s'approche. Noé dit : j'ai versé. Il prend une éponge. Il répare. Il essuie la table. L'eau disparaît. Parce qu'il a dit, il a pu réparer. Maman dit : merci. Noé souffle. Ses joues se calment. On dit. On répare.</t>
+          <t>Noé est à l'école. Maman aide pour un atelier. Noé porte un bol d'eau. Le bol penche. L'eau tombe sur la table. Noé sent ses joues chaudes. Je suis gêné. C'est une erreur. Une erreur ne dit pas qui il est. Être gêné, ce n'est pas honteux. Maman s'approche. J'ai versé. Il prend une éponge. Il répare. Il essuie la table. L'eau disparaît. Parce qu'il a dit, il a pu réparer. Merci. Noé souffle. Ses joues se calment. On dit. On répare.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Noé est à l'école. Maman aide pour un atelier. Noé porte un bol d'eau. Le bol penche. L'eau tombe sur la table. Noé sent ses joues chaudes.
+narrateur|Je suis gêné. C'est une erreur.
+narrateur|Une erreur ne dit pas qui il est. Être gêné, ce n'est pas honteux. Maman s'approche.
+enfant-m|J'ai versé.
+narrateur|Il prend une éponge. Il répare. Il essuie la table. L'eau disparaît. Parce qu'il a dit, il a pu réparer.
+maman|Merci.
+narrateur|Noé souffle. Ses joues se calment. On dit. On répare.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a versé l'eau. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a nommé : gêné. Il a dit l'erreur. Il a réparé avec l'éponge. Maman était là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1828,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose le bol. Maman pose l'éponge. Ils sourient.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1995,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.008-02.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.008-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,11 @@
 narrateur|Noé souffle. Ses joues se calment. On dit. On répare.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1509,7 @@
           <t>narrateur|Noé a versé l'eau. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1681,7 @@
           <t>narrateur|Noé a nommé : gêné. Il a dit l'erreur. Il a réparé avec l'éponge. Maman était là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1845,7 @@
           <t>narrateur|Noé pose le bol. Maman pose l'éponge. Ils sourient.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.008-02.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.008-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Noé est gêné</t>
+          <t>Raphaël est gêné</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Raphaël porte un bol d'eau à l'atelier. L'eau tombe. Il dit qu'il est gêné. Il répare avec une éponge.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Noé est à l'école. Maman aide pour un atelier. Noé porte un bol d'eau. Le bol penche. L'eau tombe sur la table. Noé sent ses joues chaudes. Je suis gêné. C'est une erreur. Une erreur ne dit pas qui il est. Être gêné, ce n'est pas honteux. Maman s'approche. J'ai versé. Il prend une éponge. Il répare. Il essuie la table. L'eau disparaît. Parce qu'il a dit, il a pu réparer. Merci. Noé souffle. Ses joues se calment. On dit. On répare.</t>
+          <t>Le couloir de l'école sent la colle. Des dessins de maisons sèchent sur une ficelle. Une feuille jaune tourne un peu. Dans la salle, les tables sont en bois clair. Une éponge bleue attend près de l'évier. Des pots de peinture sont fermés, tout ronds. La fenêtre donne sur la cour, un peu grise. Maman aide pour un atelier d'eau. Raphaël, tu portes le bol, tout doux. Jusqu'à la table, près des pinceaux. Oui, maman. Je le porte. En ce moment, Raphaël marche vers la table. Le bol d'eau est frais contre ses mains. Le bol penche. L'eau tombe sur la table. Une petite rivière brille sur le bois. Raphaël sent ses joues chaudes. Je suis gêné. C'est une erreur. Une erreur ne dit pas qui tu es. Être gêné, ce n'est pas honteux. Maman s'approche. J'ai versé. Merci d'avoir dit. Voici l'éponge. Raphaël prend l'éponge bleue. Il répare. Il essuie la table. L'eau disparaît. Parce que tu as dit, tu as pu réparer. J'ai dit. J'ai réparé. Bravo, Raphaël. C'est du bon travail. Raphaël souffle. Ses joues se calment. On dit. On répare. Tes joues sont moins chaudes ? Oui, maman. La feuille jaune ne tourne plus. L'éponge est un peu gonflée d'eau. On regarde les maisons, ensemble ? Il y a un toit rouge. Oui. Et ta table est sèche.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,20 +1324,56 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Noé est à l'école. Maman aide pour un atelier. Noé porte un bol d'eau. Le bol penche. L'eau tombe sur la table. Noé sent ses joues chaudes.
-narrateur|Je suis gêné. C'est une erreur.
-narrateur|Une erreur ne dit pas qui il est. Être gêné, ce n'est pas honteux. Maman s'approche.
+          <t>narrateur|Le couloir de l'école sent la colle.
+narrateur|Des dessins de maisons sèchent sur une ficelle.
+narrateur|Une feuille jaune tourne un peu.
+narrateur|Dans la salle, les tables sont en bois clair.
+narrateur|Une éponge bleue attend près de l'évier.
+narrateur|Des pots de peinture sont fermés, tout ronds.
+narrateur|La fenêtre donne sur la cour, un peu grise.
+narrateur|Maman aide pour un atelier d'eau.
+maman|Raphaël, tu portes le bol, tout doux.
+maman|Jusqu'à la table, près des pinceaux.
+enfant-m|Oui, maman.
+enfant-m|Je le porte.
+narrateur|En ce moment, Raphaël marche vers la table.
+narrateur|Le bol d'eau est frais contre ses mains.
+narrateur|Le bol penche.
+narrateur|L'eau tombe sur la table.
+narrateur|Une petite rivière brille sur le bois.
+narrateur|Raphaël sent ses joues chaudes.
+enfant-m|Je suis gêné.
+maman|C'est une erreur.
+maman|Une erreur ne dit pas qui tu es.
+maman|Être gêné, ce n'est pas honteux.
+narrateur|Maman s'approche.
 enfant-m|J'ai versé.
-narrateur|Il prend une éponge. Il répare. Il essuie la table. L'eau disparaît. Parce qu'il a dit, il a pu réparer.
-maman|Merci.
-narrateur|Noé souffle. Ses joues se calment. On dit. On répare.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>enfants_parc</t>
-        </is>
-      </c>
+maman|Merci d'avoir dit.
+maman|Voici l'éponge.
+narrateur|Raphaël prend l'éponge bleue.
+narrateur|Il répare.
+narrateur|Il essuie la table.
+narrateur|L'eau disparaît.
+maman|Parce que tu as dit, tu as pu réparer.
+enfant-m|J'ai dit.
+enfant-m|J'ai réparé.
+maman|Bravo, Raphaël.
+maman|C'est du bon travail.
+narrateur|Raphaël souffle.
+narrateur|Ses joues se calment.
+maman|On dit.
+maman|On répare.
+maman|Tes joues sont moins chaudes ?
+enfant-m|Oui, maman.
+narrateur|La feuille jaune ne tourne plus.
+narrateur|L'éponge est un peu gonflée d'eau.
+maman|On regarde les maisons, ensemble ?
+enfant-m|Il y a un toit rouge.
+maman|Oui.
+maman|Et ta table est sèche.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1350,7 +1398,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Noé a versé l'eau. Que fait-il ?</t>
+          <t>Raphaël a versé l'eau. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1506,7 +1554,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Noé a versé l'eau. Que fait-il ?</t>
+          <t>narrateur|Raphaël a versé l'eau.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1534,7 +1583,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Noé a nommé : gêné. Il a dit l'erreur. Il a réparé avec l'éponge. Maman était là.</t>
+          <t>Raphaël a nommé : gêné. Il a dit l'erreur. Il a réparé avec l'éponge. Je suis gêné. J'ai versé. J'ai réparé. Oui. L'erreur n'est pas toi. Bravo. C'est du bon travail. L'éponge bleue repose près de l'évier. On pose le bol, tout droit ? Oui. Tout doux. On dit. On répare. Un pinceau attend près du pot fermé.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1678,7 +1727,23 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Noé a nommé : gêné. Il a dit l'erreur. Il a réparé avec l'éponge. Maman était là.</t>
+          <t>narrateur|Raphaël a nommé : gêné.
+narrateur|Il a dit l'erreur.
+narrateur|Il a réparé avec l'éponge.
+enfant-m|Je suis gêné.
+enfant-m|J'ai versé.
+enfant-m|J'ai réparé.
+maman|Oui.
+maman|L'erreur n'est pas toi.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|L'éponge bleue repose près de l'évier.
+maman|On pose le bol, tout droit ?
+enfant-m|Oui.
+enfant-m|Tout doux.
+maman|On dit.
+maman|On répare.
+narrateur|Un pinceau attend près du pot fermé.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1706,7 +1771,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Noé pose le bol. Maman pose l'éponge. Ils sourient.</t>
+          <t>Raphaël pose le bol. Maman pose l'éponge. La table est sèche, maintenant. On peut peindre ? Oui. Un pinceau, tout doux. Tu as dit. Tu as réparé. C'est du bon travail, Raphaël. J'étais gêné. Et l'erreur n'est pas toi. Le couloir sent encore un peu la colle. Les maisons sur la ficelle restent là. La cour, derrière la vitre, reste grise. Tu prends le pinceau ? Oui. Tout doux. L'eau est dans le bol, maintenant. Je peins un toit rouge. Bravo. Tu as réparé, puis tu as peint. Le pinceau laisse un trait rouge.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,7 +1907,28 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Noé pose le bol. Maman pose l'éponge. Ils sourient.</t>
+          <t>narrateur|Raphaël pose le bol.
+narrateur|Maman pose l'éponge.
+maman|La table est sèche, maintenant.
+enfant-m|On peut peindre ?
+maman|Oui.
+maman|Un pinceau, tout doux.
+maman|Tu as dit.
+maman|Tu as réparé.
+maman|C'est du bon travail, Raphaël.
+enfant-m|J'étais gêné.
+maman|Et l'erreur n'est pas toi.
+narrateur|Le couloir sent encore un peu la colle.
+narrateur|Les maisons sur la ficelle restent là.
+narrateur|La cour, derrière la vitre, reste grise.
+maman|Tu prends le pinceau ?
+enfant-m|Oui.
+enfant-m|Tout doux.
+maman|L'eau est dans le bol, maintenant.
+enfant-m|Je peins un toit rouge.
+maman|Bravo.
+maman|Tu as réparé, puis tu as peint.
+narrateur|Le pinceau laisse un trait rouge.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1870,7 +1956,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'étais gêné. J'ai dit. J'ai réparé. Bravo, Raphaël. Tu as fait du bon travail. L'éponge bleue sèche près de l'évier. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,7 +2096,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'étais gêné.
+enfant-m|J'ai dit.
+enfant-m|J'ai réparé.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+narrateur|L'éponge bleue sèche près de l'évier.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2032,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2162,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.008-02.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.008-02.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le couloir de l'école sent la colle. Des dessins de maisons sèchent sur une ficelle. Une feuille jaune tourne un peu. Dans la salle, les tables sont en bois clair. Une éponge bleue attend près de l'évier. Des pots de peinture sont fermés, tout ronds. La fenêtre donne sur la cour, un peu grise. Maman aide pour un atelier d'eau. Raphaël, tu portes le bol, tout doux. Jusqu'à la table, près des pinceaux. Oui, maman. Je le porte. En ce moment, Raphaël marche vers la table. Le bol d'eau est frais contre ses mains. Le bol penche. L'eau tombe sur la table. Une petite rivière brille sur le bois. Raphaël sent ses joues chaudes. Je suis gêné. C'est une erreur. Une erreur ne dit pas qui tu es. Être gêné, ce n'est pas honteux. Maman s'approche. J'ai versé. Merci d'avoir dit. Voici l'éponge. Raphaël prend l'éponge bleue. Il répare. Il essuie la table. L'eau disparaît. Parce que tu as dit, tu as pu réparer. J'ai dit. J'ai réparé. Bravo, Raphaël. C'est du bon travail. Raphaël souffle. Ses joues se calment. On dit. On répare. Tes joues sont moins chaudes ? Oui, maman. La feuille jaune ne tourne plus. L'éponge est un peu gonflée d'eau. On regarde les maisons, ensemble ? Il y a un toit rouge. Oui. Et ta table est sèche.</t>
+          <t>Le couloir de l'école sent la colle. Des dessins de maisons sèchent sur une ficelle. Une feuille jaune tourne un peu. Dans la salle, les tables sont en bois clair. Une éponge bleue attend près de l'évier. Des pots de peinture sont fermés, tout ronds. La fenêtre donne sur la cour, un peu grise. Maman aide pour un atelier d'eau. Raphaël, tu portes le bol, tout doux. Jusqu'à la table, près des pinceaux. Oui, maman. Je le porte. En ce moment, Raphaël marche vers la table. Le bol d'eau est frais contre ses mains. Le bol penche. L'eau tombe sur la table. Une petite rivière brille sur le bois. Raphaël sent ses joues chaudes. Je suis gêné. C'est une erreur. Une erreur ne dit pas qui tu es. Être gêné, ce n'est pas honteux. Maman s'approche. J'ai versé. Merci d'avoir dit. Voici l'éponge. Raphaël prend l'éponge bleue. Il répare. Il essuie la table. L'eau disparaît. Parce que tu as dit, tu as pu réparer. J'ai dit. J'ai réparé. Bravo, Raphaël. Raphaël souffle. Ses joues se calment. On dit. On répare. Tes joues sont moins chaudes ? Oui, maman. La feuille jaune ne tourne plus. L'éponge est un peu gonflée d'eau. On regarde les maisons, ensemble ? Il y a un toit rouge. Oui. Et ta table est sèche.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Noé est à l'école. Maman aide pour un atelier. Noé porte un bol d'eau. Le bol penche. L'eau tombe sur la table. Noé sent ses joues chaudes. Il dit : je suis &lt;emphasis level="moderate"&gt;gêné&lt;/emphasis&gt;. C'est une erreur. Une erreur ne dit pas qui il est. Être gêné, ce n'est pas honteux. Maman s'approche. Noé dit : j'ai versé. Il prend une éponge. Il répare. Il essuie la table. L'eau disparaît. Parce qu'il a dit, il a pu réparer. Maman dit : merci. Noé souffle. Ses joues se calment. On dit. On répare.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le couloir de l'école sent la colle. Des dessins de maisons sèchent sur une ficelle. Une feuille jaune tourne un peu. Dans la salle, les tables sont en bois clair. Une éponge bleue attend près de l'évier. Des pots de peinture sont fermés, tout ronds. La fenêtre donne sur la cour, un peu grise. Maman aide pour un atelier d'eau. Raphaël, tu portes le bol, tout doux. Jusqu'à la table, près des pinceaux. Oui, maman. Je le porte. En ce moment, Raphaël marche vers la table. Le bol d'eau est frais contre ses mains. Le bol penche. L'eau tombe sur la table. Une petite rivière brille sur le bois. Raphaël sent ses joues chaudes. Je suis gêné. C'est une erreur. Une erreur ne dit pas qui tu es. Être gêné, ce n'est pas honteux. Maman s'approche. J'ai versé. Merci d'avoir dit. Voici l'éponge. Raphaël prend l'éponge bleue. Il répare. Il essuie la table. L'eau disparaît. Parce que tu as dit, tu as pu réparer. J'ai dit. J'ai réparé. Bravo, Raphaël. Raphaël souffle. Ses joues se calment. On dit. On répare. Tes joues sont moins chaudes ? Oui, maman. La feuille jaune ne tourne plus. L'éponge est un peu gonflée d'eau. On regarde les maisons, ensemble ? Il y a un toit rouge. Oui. Et ta table est sèche.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1358,7 +1358,6 @@
 enfant-m|J'ai dit.
 enfant-m|J'ai réparé.
 maman|Bravo, Raphaël.
-maman|C'est du bon travail.
 narrateur|Raphaël souffle.
 narrateur|Ses joues se calment.
 maman|On dit.
@@ -1373,7 +1372,6 @@
 maman|Et ta table est sèche.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1403,7 +1401,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Noé a versé l'eau. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a versé l'eau. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1558,7 +1556,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1583,12 +1580,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a nommé : gêné. Il a dit l'erreur. Il a réparé avec l'éponge. Je suis gêné. J'ai versé. J'ai réparé. Oui. L'erreur n'est pas toi. Bravo. C'est du bon travail. L'éponge bleue repose près de l'évier. On pose le bol, tout droit ? Oui. Tout doux. On dit. On répare. Un pinceau attend près du pot fermé.</t>
+          <t>Raphaël a nommé : gêné. Il a dit l'erreur. Il a réparé avec l'éponge. Je suis gêné. J'ai versé. J'ai réparé. Oui. L'erreur n'est pas toi. Bravo. L'éponge bleue repose près de l'évier. On pose le bol, tout droit ? Oui. Tout doux. On dit. On répare. Un pinceau attend près du pot fermé.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Noé a nommé : &lt;emphasis level="moderate"&gt;gêné&lt;/emphasis&gt;. Il a dit l'erreur. Il a réparé avec l'éponge. Maman était là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a nommé : gêné. Il a dit l'erreur. Il a réparé avec l'éponge. Je suis gêné. J'ai versé. J'ai réparé. Oui. L'erreur n'est pas toi. Bravo. L'éponge bleue repose près de l'évier. On pose le bol, tout droit ? Oui. Tout doux. On dit. On répare. Un pinceau attend près du pot fermé.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1736,7 +1733,6 @@
 maman|Oui.
 maman|L'erreur n'est pas toi.
 maman|Bravo.
-maman|C'est du bon travail.
 narrateur|L'éponge bleue repose près de l'évier.
 maman|On pose le bol, tout droit ?
 enfant-m|Oui.
@@ -1746,7 +1742,6 @@
 narrateur|Un pinceau attend près du pot fermé.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1771,12 +1766,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Raphaël pose le bol. Maman pose l'éponge. La table est sèche, maintenant. On peut peindre ? Oui. Un pinceau, tout doux. Tu as dit. Tu as réparé. C'est du bon travail, Raphaël. J'étais gêné. Et l'erreur n'est pas toi. Le couloir sent encore un peu la colle. Les maisons sur la ficelle restent là. La cour, derrière la vitre, reste grise. Tu prends le pinceau ? Oui. Tout doux. L'eau est dans le bol, maintenant. Je peins un toit rouge. Bravo. Tu as réparé, puis tu as peint. Le pinceau laisse un trait rouge.</t>
+          <t>Raphaël pose le bol. Maman pose l'éponge. La table est sèche, maintenant. On peut peindre ? Oui. Un pinceau, tout doux. Tu as dit. Tu as réparé. J'étais gêné. Et l'erreur n'est pas toi. Le couloir sent encore un peu la colle. Les maisons sur la ficelle restent là. La cour, derrière la vitre, reste grise. Tu prends le pinceau ? Oui. Tout doux. L'eau est dans le bol, maintenant. Je peins un toit rouge. Bravo. Tu as réparé, puis tu as peint. Le pinceau laisse un trait rouge.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Noé pose le bol. Maman pose l'éponge. Ils sourient.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël pose le bol. Maman pose l'éponge. La table est sèche, maintenant. On peut peindre ? Oui. Un pinceau, tout doux. Tu as dit. Tu as réparé. J'étais gêné. Et l'erreur n'est pas toi. Le couloir sent encore un peu la colle. Les maisons sur la ficelle restent là. La cour, derrière la vitre, reste grise. Tu prends le pinceau ? Oui. Tout doux. L'eau est dans le bol, maintenant. Je peins un toit rouge. Bravo. Tu as réparé, puis tu as peint. Le pinceau laisse un trait rouge.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1915,7 +1910,6 @@
 maman|Un pinceau, tout doux.
 maman|Tu as dit.
 maman|Tu as réparé.
-maman|C'est du bon travail, Raphaël.
 enfant-m|J'étais gêné.
 maman|Et l'erreur n'est pas toi.
 narrateur|Le couloir sent encore un peu la colle.
@@ -1931,7 +1925,6 @@
 narrateur|Le pinceau laisse un trait rouge.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1956,12 +1949,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'étais gêné. J'ai dit. J'ai réparé. Bravo, Raphaël. Tu as fait du bon travail. L'éponge bleue sèche près de l'évier. L'histoire est finie.</t>
+          <t>J'étais gêné. J'ai dit. J'ai réparé. Bravo, Raphaël. L'éponge bleue sèche près de l'évier.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'étais gêné. J'ai dit. J'ai réparé. Bravo, Raphaël. L'éponge bleue sèche près de l'évier.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2100,12 +2093,9 @@
 enfant-m|J'ai dit.
 enfant-m|J'ai réparé.
 maman|Bravo, Raphaël.
-maman|Tu as fait du bon travail.
-narrateur|L'éponge bleue sèche près de l'évier.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|L'éponge bleue sèche près de l'évier.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2124,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2169,6 +2159,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.008-02.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.008-02.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Noé, maman</t>
+          <t>Raphaël, maman</t>
         </is>
       </c>
     </row>
